--- a/analysis/results/city_price_correlation.xlsx
+++ b/analysis/results/city_price_correlation.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,44 +430,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>faisalabad</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>hyderabad</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>islamabad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>karachi</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lahore</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>rawalpindi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>faisalabad</t>
         </is>
@@ -464,57 +476,57 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5674</v>
+        <v>0.7053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9721</v>
+        <v>0.9314</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9721</v>
+        <v>0.9314</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9721</v>
+        <v>0.9314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9833</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>hyderabad</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5674</v>
+        <v>0.7053</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.874</v>
+        <v>0.8273</v>
       </c>
       <c r="E3" t="n">
-        <v>0.874</v>
+        <v>0.8273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.874</v>
+        <v>0.8272</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9519</v>
+        <v>0.7218</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>islamabad</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9721</v>
+        <v>0.9314</v>
       </c>
       <c r="C4" t="n">
-        <v>0.874</v>
+        <v>0.8273</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -526,20 +538,20 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9829</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>karachi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9721</v>
+        <v>0.9314</v>
       </c>
       <c r="C5" t="n">
-        <v>0.874</v>
+        <v>0.8273</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -551,20 +563,20 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9829</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>lahore</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9721</v>
+        <v>0.9314</v>
       </c>
       <c r="C6" t="n">
-        <v>0.874</v>
+        <v>0.8272</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -576,29 +588,29 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9829</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>rawalpindi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9833</v>
+        <v>0.9974</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9519</v>
+        <v>0.7218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9829</v>
+        <v>0.9311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9829</v>
+        <v>0.9311</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9829</v>
+        <v>0.9311</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -619,44 +631,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>faisalabad</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>hyderabad</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>islamabad</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>karachi</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lahore</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>rawalpindi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>faisalabad</t>
         </is>
@@ -665,57 +677,57 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7261</v>
+        <v>0.8364</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9433</v>
+        <v>0.9436</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9433</v>
+        <v>0.9436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9433</v>
+        <v>0.9436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9454</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>hyderabad</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7261</v>
+        <v>0.8364</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.892</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.892</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8919</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9213</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>islamabad</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9433</v>
+        <v>0.9436</v>
       </c>
       <c r="C4" t="n">
-        <v>0.892</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -727,20 +739,20 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9234</v>
+        <v>0.9103</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>karachi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9433</v>
+        <v>0.9436</v>
       </c>
       <c r="C5" t="n">
-        <v>0.892</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -752,20 +764,20 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9234</v>
+        <v>0.9103</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>lahore</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9433</v>
+        <v>0.9436</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8919</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -777,29 +789,29 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9234</v>
+        <v>0.9103</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>rawalpindi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9454</v>
+        <v>0.9748</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9213</v>
+        <v>0.8472</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9234</v>
+        <v>0.9103</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9234</v>
+        <v>0.9103</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9234</v>
+        <v>0.9103</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>

--- a/analysis/results/city_price_correlation.xlsx
+++ b/analysis/results/city_price_correlation.xlsx
@@ -479,16 +479,16 @@
         <v>0.7053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9314</v>
+        <v>0.925</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9314</v>
+        <v>0.925</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9314</v>
+        <v>0.925</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9974</v>
+        <v>0.9703000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -504,16 +504,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8273</v>
+        <v>0.8272</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8273</v>
+        <v>0.8272</v>
       </c>
       <c r="F3" t="n">
         <v>0.8272</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7218</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="4">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9314</v>
+        <v>0.925</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8273</v>
+        <v>0.8272</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9311</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="5">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9314</v>
+        <v>0.925</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8273</v>
+        <v>0.8272</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9311</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9314</v>
+        <v>0.925</v>
       </c>
       <c r="C6" t="n">
         <v>0.8272</v>
@@ -588,7 +588,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9311</v>
+        <v>0.8758</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9974</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7218</v>
+        <v>0.7219</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9311</v>
+        <v>0.8758</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9311</v>
+        <v>0.8758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9311</v>
+        <v>0.8758</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -677,19 +677,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8364</v>
+        <v>0.8366</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9436</v>
+        <v>0.8762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9436</v>
+        <v>0.8762</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9436</v>
+        <v>0.8762</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9748</v>
+        <v>0.9764</v>
       </c>
     </row>
     <row r="3">
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8364</v>
+        <v>0.8366</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9035</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8472</v>
+        <v>0.8483000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9436</v>
+        <v>0.8762</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9103</v>
+        <v>0.9127999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9436</v>
+        <v>0.8762</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9103</v>
+        <v>0.9127999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9436</v>
+        <v>0.8762</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9035</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -789,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9103</v>
+        <v>0.9127999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9748</v>
+        <v>0.9764</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8472</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9103</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9103</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9103</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
